--- a/Database Development Spreadsheet.xlsx
+++ b/Database Development Spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trupe\source\repos\Databases\Database-Assignment-2-Individual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03ACC22F-5CEF-4DE8-BF8C-D2F9C8DC5465}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFFE27C-9D45-43DD-884B-9B199A127896}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="69">
   <si>
     <t>accounts</t>
   </si>
@@ -45,9 +45,6 @@
     <t>pk_accounts</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>VARCHAR2(20)</t>
   </si>
   <si>
@@ -93,9 +90,6 @@
     <t>VARCHAR2(8)</t>
   </si>
   <si>
-    <t>NUMBER(10)</t>
-  </si>
-  <si>
     <t>NUMBER(4)</t>
   </si>
   <si>
@@ -117,15 +111,6 @@
     <t>manager_id</t>
   </si>
   <si>
-    <t>pk_account_managers</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>account_id</t>
-  </si>
-  <si>
     <t>invoice_id</t>
   </si>
   <si>
@@ -138,9 +123,6 @@
     <t>invoice_total</t>
   </si>
   <si>
-    <t>pk_invoices</t>
-  </si>
-  <si>
     <t>fk_i_accounts</t>
   </si>
   <si>
@@ -157,13 +139,106 @@
   </si>
   <si>
     <t>invoice_items</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>NUMBER(3)</t>
+  </si>
+  <si>
+    <t>NUMBER(8,2)</t>
+  </si>
+  <si>
+    <t>NUMBER(10,2)</t>
+  </si>
+  <si>
+    <t>pk_invoice_items, fk_it_invoices</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>pk_account_managers, INCREMENTS 1 START 1000</t>
+  </si>
+  <si>
+    <t>pk_invoices, INCREMENT 1 START 10000000</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>pk_invoice_items, fk_it_products</t>
+  </si>
+  <si>
+    <t>total_price</t>
+  </si>
+  <si>
+    <t>customer_cards</t>
+  </si>
+  <si>
+    <t>card_number</t>
+  </si>
+  <si>
+    <t>NUMBER(16)</t>
+  </si>
+  <si>
+    <t>bank</t>
+  </si>
+  <si>
+    <t>security_code</t>
+  </si>
+  <si>
+    <t>fk_cc_accounts</t>
+  </si>
+  <si>
+    <t>account_number</t>
+  </si>
+  <si>
+    <t>sort_code</t>
+  </si>
+  <si>
+    <t>CHAR(8)</t>
+  </si>
+  <si>
+    <t>products</t>
+  </si>
+  <si>
+    <t>payments</t>
+  </si>
+  <si>
+    <t>pk_payments, fp_p_invoices</t>
+  </si>
+  <si>
+    <t>pk_payments, fp_p_customer_cards</t>
+  </si>
+  <si>
+    <t>pk_products, INCREMENT 1 START 10000000</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>product_description</t>
+  </si>
+  <si>
+    <t>VARCHAR(15)</t>
+  </si>
+  <si>
+    <t>VARCHAR(80)</t>
+  </si>
+  <si>
+    <t>NOT NULL, UNIQUE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,16 +246,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -188,23 +288,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="1" builtinId="29"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -483,271 +692,571 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="10"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="10"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="10"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="13"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="10"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="11"/>
+      <c r="D36" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="9"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="10"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="D43" s="13"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="9"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B47" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="10"/>
+    </row>
+    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="9"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B51" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C51" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D51" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="52" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="C52" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D52" s="10"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
